--- a/data/por_departamento/Cuscatlán/establecimientos_salud.xlsx
+++ b/data/por_departamento/Cuscatlán/establecimientos_salud.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Establecimientos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Establecimientos'!$A$1:$AA$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Establecimientos'!$A$1:$AA$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA33"/>
+  <dimension ref="A1:AA25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1461,7 +1461,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>geofabrik-way-398620394</t>
+          <t>geofabrik-way-499551477</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1471,32 +1471,32 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>way/398620394</t>
+          <t>way/499551477</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Clínica Medica</t>
+          <t>Hospital Nacional General de Cojutepeque</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Edificio</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>edificio</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1521,17 +1521,17 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>13.72392967</t>
+          <t>13.725988</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-88.94330554</t>
+          <t>-88.94221606</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -1541,39 +1541,39 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.9433425 13.7238898, -88.9433337 13.7239758, -88.9432686 13.7239696, -88.9432774 13.7238835, -88.9433425 13.7238898))</t>
+          <t>POLYGON ((-88.9427798 13.7262415, -88.9427054 13.7264856, -88.9421533 13.7263309, -88.9420188 13.7264134, -88.9417392 13.7261453, -88.9418985 13.7259768, -88.9418525 13.7257533, -88.9418171 13.7253614, -88.9420471 13.725327, -88.9421427 13.7257705, -88.9423391 13.7256038, -88.942486 13.7257533, -88.9426824 13.7259991, -88.9425249 13.7261624, -88.9427798 13.7262415))</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/398620394</t>
+          <t>https://www.openstreetmap.org/way/499551477</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.72392967,-88.94330554</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.725988,-88.94221606</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>geofabrik-way-400047365</t>
+          <t>hot-way-768458851</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>way/400047365</t>
+          <t>way/768458851</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CM Imágenes Médicas</t>
+          <t>Unidad de Salud de San Emigdio</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Polígono</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>poligono</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Cojutepeque</t>
+          <t>Santa Cruz Analquito</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1611,6 +1611,11 @@
           <t>Paracentral</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>San Emigdio</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>Polygon</t>
@@ -1618,17 +1623,17 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>13.72140838</t>
+          <t>13.64872325</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-88.93349317</t>
+          <t>-88.97632401</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -1638,59 +1643,59 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.9335387 13.7213672, -88.9335015 13.7214684, -88.9334473 13.7214496, -88.9334855 13.7213479, -88.9335387 13.7213672))</t>
+          <t>POLYGON ((-88.9764492 13.6487588, -88.9763021 13.6488198, -88.9762244 13.6486428, -88.976298 13.6486123, -88.9763513 13.6487336, -88.9764248 13.6487031, -88.9764492 13.6487588))</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/400047365</t>
+          <t>https://www.openstreetmap.org/way/768458851</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.72140838,-88.93349317</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64872325,-88.97632401</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>geofabrik-way-400059797</t>
+          <t>hot-node-9963368935</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>way/400059797</t>
+          <t>node/9963368935</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Clínica Médica Familiar</t>
+          <t>Casa de salud</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1700,7 +1705,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Monte San Juan</t>
+          <t>Cojutepeque</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1708,66 +1713,81 @@
           <t>Paracentral</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>san Ramón</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Público</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Medicina general</t>
+        </is>
+      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>13.72466401</t>
+          <t>13.7030603</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-88.93430862</t>
+          <t>-88.9181225</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.934374 13.724615, -88.9343681 13.7247197, -88.9342432 13.724713, -88.9342492 13.7246083, -88.934374 13.724615))</t>
+          <t>POINT (-88.9181225 13.7030603)</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/400059797</t>
+          <t>https://www.openstreetmap.org/node/9963368935</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.72466401,-88.93430862</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7030603,-88.9181225</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>geofabrik-way-666573509</t>
+          <t>hot-node-6340276686</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>way/666573509</t>
+          <t>node/6340276686</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Unidad Médica ISSS</t>
+          <t>UCSF San Ramón</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1782,12 +1802,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>predio</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1797,7 +1817,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Monte San Juan</t>
+          <t>San Ramón</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1805,86 +1825,91 @@
           <t>Paracentral</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>San Ramón</t>
+        </is>
+      </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>13.72523994</t>
+          <t>13.6839188</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-88.93813287</t>
+          <t>-88.9271735</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.9382634 13.7253244, -88.9380399 13.7253374, -88.9380349 13.7252552, -88.9379893 13.7252578, -88.9379836 13.7251646, -88.9382526 13.725149, -88.9382634 13.7253244))</t>
+          <t>POINT (-88.9271735 13.6839188)</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/666573509</t>
+          <t>https://www.openstreetmap.org/node/6340276686</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.72523994,-88.93813287</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6839188,-88.9271735</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>geofabrik-way-499551477</t>
+          <t>hot-node-11308525321</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>geofabrik</t>
+          <t>hot</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>way/499551477</t>
+          <t>node/11308525321</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hospital Nacional General de Cojutepeque</t>
+          <t>Medicentro Guayabal</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Consultorio</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>consultorio</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Edificio</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>edificio</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1894,7 +1919,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Monte San Juan</t>
+          <t>San José Guayabal</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1902,51 +1927,56 @@
           <t>Paracentral</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>San José Guayabal</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>13.725988</t>
+          <t>13.8388419</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-88.94221606</t>
+          <t>-89.0949608</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.9427798 13.7262415, -88.9427054 13.7264856, -88.9421533 13.7263309, -88.9420188 13.7264134, -88.9417392 13.7261453, -88.9418985 13.7259768, -88.9418525 13.7257533, -88.9418171 13.7253614, -88.9420471 13.725327, -88.9421427 13.7257705, -88.9423391 13.7256038, -88.942486 13.7257533, -88.9426824 13.7259991, -88.9425249 13.7261624, -88.9427798 13.7262415))</t>
+          <t>POINT (-89.0949608 13.8388419)</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/499551477</t>
+          <t>https://www.openstreetmap.org/node/11308525321</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.725988,-88.94221606</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8388419,-89.0949608</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hot-way-400047365</t>
+          <t>hot-node-11308351317</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1956,32 +1986,32 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>way/400047365</t>
+          <t>node/11308351317</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CM Imágenes Médicas</t>
+          <t>Unidad de Salud de San Jose Guayabal</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>poligono</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1991,7 +2021,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Monte San Juan</t>
+          <t>San José Guayabal</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2001,54 +2031,54 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Cojutepeque</t>
+          <t>San José Guayabal</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>13.72140838</t>
+          <t>13.8394552</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-88.93349317</t>
+          <t>-89.095418</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.9335015 13.7214684, -88.9335387 13.7213672, -88.9334855 13.7213479, -88.9334473 13.7214496, -88.9335015 13.7214684))</t>
+          <t>POINT (-89.095418 13.8394552)</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/400047365</t>
+          <t>https://www.openstreetmap.org/node/11308351317</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.72140838,-88.93349317</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8394552,-89.095418</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>hot-way-768458851</t>
+          <t>hot-node-11304781288</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2058,32 +2088,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>way/768458851</t>
+          <t>node/11304781288</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Unidad de Salud de San Emigdio</t>
+          <t>acunación COVID-19 - Hospital Nacional de Suchitoto</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>poligono</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2093,7 +2123,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Santa Cruz Analquito</t>
+          <t>Suchitoto</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2103,54 +2133,54 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>San Emigdio</t>
+          <t>Av. José Maria Peña Fernández, Suchitoto</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>13.64872325</t>
+          <t>13.9338102</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-88.97632401</t>
+          <t>-89.0288622</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.9764492 13.6487588, -88.9763021 13.6488198, -88.9762244 13.6486428, -88.976298 13.6486123, -88.9763513 13.6487336, -88.9764248 13.6487031, -88.9764492 13.6487588))</t>
+          <t>POINT (-89.0288622 13.9338102)</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/768458851</t>
+          <t>https://www.openstreetmap.org/node/11304781288</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.64872325,-88.97632401</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9338102,-89.0288622</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>hot-way-666573509</t>
+          <t>hot-node-11304472216</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2160,32 +2190,32 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>way/666573509</t>
+          <t>node/11304472216</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Unidad Médica ISSS</t>
+          <t>Unidad de Salud Suchitoto</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>poligono</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2195,7 +2225,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Monte San Juan</t>
+          <t>Suchitoto</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2203,61 +2233,51 @@
           <t>Paracentral</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Cuscatancingo</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>13.72523994</t>
+          <t>13.9352034</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-88.93813287</t>
+          <t>-89.0265411</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.9382634 13.7253244, -88.9380399 13.7253374, -88.9380349 13.7252552, -88.9379893 13.7252578, -88.9379836 13.7251646, -88.9382526 13.725149, -88.9382634 13.7253244))</t>
+          <t>POINT (-89.0265411 13.9352034)</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/666573509</t>
+          <t>https://www.openstreetmap.org/node/11304472216</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.72523994,-88.93813287</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9352034,-89.0265411</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>hot-way-400059797</t>
+          <t>hot-node-11304709178</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2267,32 +2287,32 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>way/400059797</t>
+          <t>node/11304709178</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Clínica Médica Familiar</t>
+          <t>Clinica Medica ASUSA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>poligono</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2302,7 +2322,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Monte San Juan</t>
+          <t>Suchitoto</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2312,54 +2332,54 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Cojutepeque</t>
+          <t>Suchitoto</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>13.72466401</t>
+          <t>13.9360492</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-88.93430862</t>
+          <t>-89.0269682</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.934374 13.724615, -88.9342492 13.7246083, -88.9342432 13.724713, -88.9343681 13.7247197, -88.934374 13.724615))</t>
+          <t>POINT (-89.0269682 13.9360492)</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/400059797</t>
+          <t>https://www.openstreetmap.org/node/11304709178</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.72466401,-88.93430862</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9360492,-89.0269682</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>hot-way-398620394</t>
+          <t>hot-node-4026793686</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2369,7 +2389,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>way/398620394</t>
+          <t>node/4026793686</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2389,12 +2409,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Polígono</t>
+          <t>Punto</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>poligono</t>
+          <t>punto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2404,7 +2424,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Monte San Juan</t>
+          <t>Suchitoto</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2414,54 +2434,54 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Cojutepeque</t>
+          <t>Suchitoto</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Polygon</t>
+          <t>Point</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>13.72392967</t>
+          <t>13.9361139</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-88.94330554</t>
+          <t>-89.027083</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>centroide_area</t>
+          <t>coordenada_original</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>POLYGON ((-88.9433337 13.7239758, -88.9433425 13.7238898, -88.9432774 13.7238835, -88.9432686 13.7239696, -88.9433337 13.7239758))</t>
+          <t>POINT (-89.027083 13.9361139)</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/398620394</t>
+          <t>https://www.openstreetmap.org/node/4026793686</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.72392967,-88.94330554</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9361139,-89.027083</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>hot-node-9963368935</t>
+          <t>hot-node-10246880609</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2471,22 +2491,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>node/9963368935</t>
+          <t>node/10246880609</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Casa de salud</t>
+          <t>Unidad de Salud Intermedia Paraíso de Osorio</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2506,7 +2526,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Cojutepeque</t>
+          <t>Santa Cruz Analquito</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2514,21 +2534,6 @@
           <t>Paracentral</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>san Ramón</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Público</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Medicina general</t>
-        </is>
-      </c>
       <c r="T21" t="inlineStr">
         <is>
           <t>Point</t>
@@ -2541,12 +2546,12 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>13.7030603</t>
+          <t>13.6358453</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-88.9181225</t>
+          <t>-88.9647208</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -2556,24 +2561,24 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>POINT (-88.9181225 13.7030603)</t>
+          <t>POINT (-88.9647208 13.6358453)</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9963368935</t>
+          <t>https://www.openstreetmap.org/node/10246880609</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7030603,-88.9181225</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6358453,-88.9647208</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>hot-node-6340276686</t>
+          <t>hot-node-11316885275</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2583,22 +2588,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>node/6340276686</t>
+          <t>node/11316885275</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>UCSF San Ramón</t>
+          <t>Unidad de Salud | San Rafael Cedros</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Clínica</t>
+          <t>Consultorio</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>clinica</t>
+          <t>consultorio</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -2618,7 +2623,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>San Rafael Cedros</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2628,7 +2633,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>San Ramón</t>
+          <t>San Rafael Cedros</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2643,12 +2648,12 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>13.6839188</t>
+          <t>13.730832</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-88.9271735</t>
+          <t>-88.8824927</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -2658,24 +2663,24 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>POINT (-88.9271735 13.6839188)</t>
+          <t>POINT (-88.8824927 13.730832)</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/6340276686</t>
+          <t>https://www.openstreetmap.org/node/11316885275</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6839188,-88.9271735</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.730832,-88.8824927</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>hot-node-11308525321</t>
+          <t>hot-node-13202878448</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2685,22 +2690,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>node/11308525321</t>
+          <t>node/13202878448</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Medicentro Guayabal</t>
+          <t>Hospital Rosendo Alvarenga</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Consultorio</t>
+          <t>Hospital</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>consultorio</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2720,7 +2725,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>San José Guayabal</t>
+          <t>Monte San Juan</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2728,11 +2733,6 @@
           <t>Paracentral</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>San José Guayabal</t>
-        </is>
-      </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>Point</t>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>13.8388419</t>
+          <t>13.7266021</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-89.0949608</t>
+          <t>-88.9344165</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -2760,24 +2760,24 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>POINT (-89.0949608 13.8388419)</t>
+          <t>POINT (-88.9344165 13.7266021)</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/11308525321</t>
+          <t>https://www.openstreetmap.org/node/13202878448</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8388419,-89.0949608</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7266021,-88.9344165</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>hot-node-11308351317</t>
+          <t>hot-node-6340464889</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2787,22 +2787,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>node/11308351317</t>
+          <t>node/6340464889</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Unidad de Salud de San Jose Guayabal</t>
+          <t>Cruz Roja Salvadoreña Seccional Cojutepeque</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>San José Guayabal</t>
+          <t>Monte San Juan</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2830,11 +2830,6 @@
           <t>Paracentral</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>San José Guayabal</t>
-        </is>
-      </c>
       <c r="T24" t="inlineStr">
         <is>
           <t>Point</t>
@@ -2847,12 +2842,12 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>13.8394552</t>
+          <t>13.7249161</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-89.095418</t>
+          <t>-88.9400073</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -2862,24 +2857,24 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>POINT (-89.095418 13.8394552)</t>
+          <t>POINT (-88.9400073 13.7249161)</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/11308351317</t>
+          <t>https://www.openstreetmap.org/node/6340464889</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.8394552,-89.095418</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7249161,-88.9400073</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hot-node-11304781288</t>
+          <t>hot-node-6901156582</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2889,22 +2884,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>node/11304781288</t>
+          <t>node/6901156582</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>acunación COVID-19 - Hospital Nacional de Suchitoto</t>
+          <t>UCSF Monte San Juan</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Clínica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>hospital</t>
+          <t>clinica</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2924,7 +2919,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Suchitoto</t>
+          <t>Monte San Juan</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2934,7 +2929,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Av. José Maria Peña Fernández, Suchitoto</t>
+          <t>Monte San Juan</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -2949,12 +2944,12 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>13.9338102</t>
+          <t>13.7618991</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-89.0288622</t>
+          <t>-88.9506613</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -2964,818 +2959,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>POINT (-89.0288622 13.9338102)</t>
+          <t>POINT (-88.9506613 13.7618991)</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/11304781288</t>
+          <t>https://www.openstreetmap.org/node/6901156582</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9338102,-89.0288622</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>hot-node-11304472216</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>node/11304472216</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Unidad de Salud Suchitoto</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Hospital</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Cuscatlán</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Suchitoto</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>13.9352034</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>-89.0265411</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>POINT (-89.0265411 13.9352034)</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/11304472216</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9352034,-89.0265411</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>hot-node-11304709178</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>node/11304709178</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Clinica Medica ASUSA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Hospital</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Cuscatlán</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Suchitoto</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Suchitoto</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>13.9360492</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>-89.0269682</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>POINT (-89.0269682 13.9360492)</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/11304709178</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9360492,-89.0269682</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>hot-node-4026793686</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>node/4026793686</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Clínica Medica</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Cuscatlán</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Suchitoto</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Suchitoto</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>13.9361139</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>-89.027083</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>POINT (-89.027083 13.9361139)</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/4026793686</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.9361139,-89.027083</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>hot-node-10246880609</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>node/10246880609</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Unidad de Salud Intermedia Paraíso de Osorio</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Cuscatlán</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Santa Cruz Analquito</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>13.6358453</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>-88.9647208</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>POINT (-88.9647208 13.6358453)</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/10246880609</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.6358453,-88.9647208</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>hot-node-11316885275</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>node/11316885275</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Unidad de Salud | San Rafael Cedros</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Consultorio</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>consultorio</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Cuscatlán</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>San Rafael Cedros</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>San Rafael Cedros</t>
-        </is>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>13.730832</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>-88.8824927</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>POINT (-88.8824927 13.730832)</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/11316885275</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.730832,-88.8824927</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>hot-node-13202878448</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>node/13202878448</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Hospital Rosendo Alvarenga</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Hospital</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>hospital</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Cuscatlán</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Monte San Juan</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>13.7266021</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>-88.9344165</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>POINT (-88.9344165 13.7266021)</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/13202878448</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7266021,-88.9344165</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>hot-node-6340464889</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>node/6340464889</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Cruz Roja Salvadoreña Seccional Cojutepeque</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Cuscatlán</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Monte San Juan</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>13.7249161</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>-88.9400073</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>POINT (-88.9400073 13.7249161)</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/6340464889</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=13.7249161,-88.9400073</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>hot-node-6901156582</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>hot</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>node/6901156582</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>UCSF Monte San Juan</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Clínica</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>clinica</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Punto</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>punto</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Cuscatlán</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Monte San Juan</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Paracentral</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Monte San Juan</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Point</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>13.7618991</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>-88.9506613</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>coordenada_original</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>POINT (-88.9506613 13.7618991)</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/6901156582</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
         <is>
           <t>https://www.google.com/maps/search/?api=1&amp;query=13.7618991,-88.9506613</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA33"/>
+  <autoFilter ref="A1:AA25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>